--- a/2nd_round_screening/Solubility_result.xlsx
+++ b/2nd_round_screening/Solubility_result.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zeqing/Library/CloudStorage/Dropbox/Acceleration_consortium/Projects/SDL_workflow_development/sdlnano/20250401_code/2nd_round_screening/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zeqing/0_Github/SDL5_Nano/2nd_round_screening/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBD8B79F-E0EC-5D40-88E7-ADDCD3711889}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6F5DFC0-55DB-9949-9938-DF3AAE82BE42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2180" yWindow="760" windowWidth="28060" windowHeight="17440" xr2:uid="{1B93A286-1A04-C646-B222-41A0E8FAD01F}"/>
+    <workbookView xWindow="3580" yWindow="760" windowWidth="30240" windowHeight="17760" activeTab="1" xr2:uid="{1B93A286-1A04-C646-B222-41A0E8FAD01F}"/>
   </bookViews>
   <sheets>
     <sheet name="sample" sheetId="1" r:id="rId1"/>
@@ -244,10 +244,10 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>standard!$A$2:$A$9</c:f>
+              <c:f>standard!$A$2:$A$10</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -270,6 +270,9 @@
                   <c:v>100</c:v>
                 </c:pt>
                 <c:pt idx="7">
+                  <c:v>250</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>500</c:v>
                 </c:pt>
               </c:numCache>
@@ -277,33 +280,36 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>standard!$B$2:$B$9</c:f>
+              <c:f>standard!$B$2:$B$10</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>21.558</c:v>
+                  <c:v>17.521999999999998</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>48.466000000000001</c:v>
+                  <c:v>36.381</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>94.757000000000005</c:v>
+                  <c:v>98.662000000000006</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>196.08099999999999</c:v>
+                  <c:v>206.548</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>469.84800000000001</c:v>
+                  <c:v>521.18399999999997</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>915.255</c:v>
+                  <c:v>1074.355</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1838.3109999999999</c:v>
+                  <c:v>2136.6</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>8983.7710000000006</c:v>
+                  <c:v>5092.2259999999997</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9989.6059999999998</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -460,6 +466,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -467,7 +474,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1064,13 +1070,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>692150</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>101600</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>311150</xdr:colOff>
-      <xdr:row>22</xdr:row>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>88900</xdr:colOff>
+      <xdr:row>23</xdr:row>
       <xdr:rowOff>120650</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -1416,7 +1422,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD656113-46D1-4A46-8A6F-049C2C49A62C}">
-  <dimension ref="A1:C61"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
@@ -1435,7 +1441,7 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>181.18199999999999</v>
+        <v>886.327</v>
       </c>
       <c r="C2">
         <v>2.7</v>
@@ -1444,7 +1450,7 @@
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" s="1"/>
       <c r="B3">
-        <v>199.12799999999999</v>
+        <v>835.351</v>
       </c>
       <c r="C3">
         <v>2.7</v>
@@ -1453,7 +1459,7 @@
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="1"/>
       <c r="B4">
-        <v>251.346</v>
+        <v>840.03099999999995</v>
       </c>
       <c r="C4">
         <v>2.7</v>
@@ -1464,7 +1470,7 @@
         <v>1</v>
       </c>
       <c r="B5">
-        <v>2009.0039999999999</v>
+        <v>856.85900000000004</v>
       </c>
       <c r="C5">
         <v>2.7</v>
@@ -1473,7 +1479,7 @@
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="1"/>
       <c r="B6">
-        <v>1995.6990000000001</v>
+        <v>833.21699999999998</v>
       </c>
       <c r="C6">
         <v>2.7</v>
@@ -1482,7 +1488,7 @@
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" s="1"/>
       <c r="B7">
-        <v>2116.3049999999998</v>
+        <v>829.99699999999996</v>
       </c>
       <c r="C7">
         <v>2.7</v>
@@ -1493,7 +1499,7 @@
         <v>2</v>
       </c>
       <c r="B8">
-        <v>1732.4649999999999</v>
+        <v>839.01400000000001</v>
       </c>
       <c r="C8">
         <v>2.7</v>
@@ -1502,7 +1508,7 @@
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" s="1"/>
       <c r="B9">
-        <v>1728.5650000000001</v>
+        <v>814.62199999999996</v>
       </c>
       <c r="C9">
         <v>2.7</v>
@@ -1511,7 +1517,7 @@
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="1"/>
       <c r="B10">
-        <v>1714.9190000000001</v>
+        <v>823.96600000000001</v>
       </c>
       <c r="C10">
         <v>2.7</v>
@@ -1522,7 +1528,7 @@
         <v>3</v>
       </c>
       <c r="B11">
-        <v>2070.6570000000002</v>
+        <v>1248.7170000000001</v>
       </c>
       <c r="C11">
         <v>2.7</v>
@@ -1531,7 +1537,7 @@
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" s="1"/>
       <c r="B12">
-        <v>2014.896</v>
+        <v>1313.8910000000001</v>
       </c>
       <c r="C12">
         <v>2.7</v>
@@ -1540,7 +1546,7 @@
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="1"/>
       <c r="B13">
-        <v>2083.6970000000001</v>
+        <v>1206.251</v>
       </c>
       <c r="C13">
         <v>2.7</v>
@@ -1551,7 +1557,7 @@
         <v>4</v>
       </c>
       <c r="B14">
-        <v>1822.39</v>
+        <v>1411.8320000000001</v>
       </c>
       <c r="C14">
         <v>2.7</v>
@@ -1560,7 +1566,7 @@
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" s="1"/>
       <c r="B15">
-        <v>1781.259</v>
+        <v>1355.453</v>
       </c>
       <c r="C15">
         <v>2.7</v>
@@ -1569,7 +1575,7 @@
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" s="1"/>
       <c r="B16">
-        <v>1772.338</v>
+        <v>1351.5239999999999</v>
       </c>
       <c r="C16">
         <v>2.7</v>
@@ -1580,7 +1586,7 @@
         <v>5</v>
       </c>
       <c r="B17">
-        <v>1768.5940000000001</v>
+        <v>1393.951</v>
       </c>
       <c r="C17">
         <v>2.7</v>
@@ -1589,7 +1595,7 @@
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" s="1"/>
       <c r="B18">
-        <v>1749.269</v>
+        <v>1392.075</v>
       </c>
       <c r="C18">
         <v>2.7</v>
@@ -1598,7 +1604,7 @@
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" s="1"/>
       <c r="B19">
-        <v>1737.0719999999999</v>
+        <v>1380.4749999999999</v>
       </c>
       <c r="C19">
         <v>2.7</v>
@@ -1609,7 +1615,7 @@
         <v>6</v>
       </c>
       <c r="B20">
-        <v>1020.4690000000001</v>
+        <v>1818.9570000000001</v>
       </c>
       <c r="C20">
         <v>2.7</v>
@@ -1618,7 +1624,7 @@
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" s="1"/>
       <c r="B21">
-        <v>978.78300000000002</v>
+        <v>1796.8340000000001</v>
       </c>
       <c r="C21">
         <v>2.7</v>
@@ -1627,7 +1633,7 @@
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" s="1"/>
       <c r="B22">
-        <v>996.34699999999998</v>
+        <v>1859.6020000000001</v>
       </c>
       <c r="C22">
         <v>2.7</v>
@@ -1638,7 +1644,7 @@
         <v>7</v>
       </c>
       <c r="B23">
-        <v>2097.6959999999999</v>
+        <v>1894.4380000000001</v>
       </c>
       <c r="C23">
         <v>2.7</v>
@@ -1647,7 +1653,7 @@
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="1"/>
       <c r="B24">
-        <v>2079.2060000000001</v>
+        <v>1871.29</v>
       </c>
       <c r="C24">
         <v>2.7</v>
@@ -1656,7 +1662,7 @@
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" s="1"/>
       <c r="B25">
-        <v>2085.6280000000002</v>
+        <v>1880.0319999999999</v>
       </c>
       <c r="C25">
         <v>2.7</v>
@@ -1667,7 +1673,7 @@
         <v>8</v>
       </c>
       <c r="B26">
-        <v>1857.989</v>
+        <v>1902.1890000000001</v>
       </c>
       <c r="C26">
         <v>2.7</v>
@@ -1676,7 +1682,7 @@
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" s="1"/>
       <c r="B27">
-        <v>1813.2829999999999</v>
+        <v>1880.1980000000001</v>
       </c>
       <c r="C27">
         <v>2.7</v>
@@ -1685,353 +1691,23 @@
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" s="1"/>
       <c r="B28">
-        <v>1835.011</v>
+        <v>1852.0809999999999</v>
       </c>
       <c r="C28">
         <v>2.7</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A29" s="1">
-        <v>9</v>
-      </c>
-      <c r="B29">
-        <v>1865.6780000000001</v>
-      </c>
-      <c r="C29">
-        <v>2.7</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A30" s="1"/>
-      <c r="B30">
-        <v>1793.57</v>
-      </c>
-      <c r="C30">
-        <v>2.7</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A31" s="1"/>
-      <c r="B31">
-        <v>1873.9190000000001</v>
-      </c>
-      <c r="C31">
-        <v>2.7</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A32" s="1">
-        <v>10</v>
-      </c>
-      <c r="B32">
-        <v>1012.285</v>
-      </c>
-      <c r="C32">
-        <v>2.7</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A33" s="1"/>
-      <c r="B33">
-        <v>990.67700000000002</v>
-      </c>
-      <c r="C33">
-        <v>2.7</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A34" s="1"/>
-      <c r="B34">
-        <v>997.25800000000004</v>
-      </c>
-      <c r="C34">
-        <v>2.7</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A35" s="1">
-        <v>11</v>
-      </c>
-      <c r="B35">
-        <v>1018.49</v>
-      </c>
-      <c r="C35">
-        <v>2.7</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A36" s="1"/>
-      <c r="B36">
-        <v>1011.829</v>
-      </c>
-      <c r="C36">
-        <v>2.7</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A37" s="1"/>
-      <c r="B37">
-        <v>1034.73</v>
-      </c>
-      <c r="C37">
-        <v>2.7</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A38" s="1">
-        <v>12</v>
-      </c>
-      <c r="B38">
-        <v>722.16300000000001</v>
-      </c>
-      <c r="C38">
-        <v>2.7</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A39" s="1"/>
-      <c r="B39">
-        <v>713.69200000000001</v>
-      </c>
-      <c r="C39">
-        <v>2.7</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A40" s="1"/>
-      <c r="B40">
-        <v>735.53300000000002</v>
-      </c>
-      <c r="C40">
-        <v>2.7</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A41" s="1">
-        <v>13</v>
-      </c>
-      <c r="B41">
-        <v>1789.2380000000001</v>
-      </c>
-      <c r="C41">
-        <v>2.7</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A42" s="1"/>
-      <c r="B42">
-        <v>1751.4549999999999</v>
-      </c>
-      <c r="C42">
-        <v>2.7</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A43" s="1"/>
-      <c r="B43">
-        <v>1774.7719999999999</v>
-      </c>
-      <c r="C43">
-        <v>2.7</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A44" s="1">
-        <v>14</v>
-      </c>
-      <c r="B44">
-        <v>1015.8869999999999</v>
-      </c>
-      <c r="C44">
-        <v>2.7</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A45" s="1"/>
-      <c r="B45">
-        <v>996.35900000000004</v>
-      </c>
-      <c r="C45">
-        <v>2.7</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A46" s="1"/>
-      <c r="B46">
-        <v>1025.5450000000001</v>
-      </c>
-      <c r="C46">
-        <v>2.7</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A47" s="1">
-        <v>15</v>
-      </c>
-      <c r="B47">
-        <v>1039.5920000000001</v>
-      </c>
-      <c r="C47">
-        <v>2.7</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A48" s="1"/>
-      <c r="B48">
-        <v>1030.5999999999999</v>
-      </c>
-      <c r="C48">
-        <v>2.7</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A49" s="1"/>
-      <c r="B49">
-        <v>1041.201</v>
-      </c>
-      <c r="C49">
-        <v>2.7</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A50" s="1">
-        <v>16</v>
-      </c>
-      <c r="B50">
-        <v>735.00400000000002</v>
-      </c>
-      <c r="C50">
-        <v>2.7</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A51" s="1"/>
-      <c r="B51">
-        <v>717.73800000000006</v>
-      </c>
-      <c r="C51">
-        <v>2.7</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A52" s="1"/>
-      <c r="B52">
-        <v>717.64700000000005</v>
-      </c>
-      <c r="C52">
-        <v>2.7</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A53" s="1">
-        <v>17</v>
-      </c>
-      <c r="B53">
-        <v>1064.0930000000001</v>
-      </c>
-      <c r="C53">
-        <v>2.7</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A54" s="1"/>
-      <c r="B54">
-        <v>1048.136</v>
-      </c>
-      <c r="C54">
-        <v>2.7</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A55" s="1"/>
-      <c r="B55">
-        <v>1045.787</v>
-      </c>
-      <c r="C55">
-        <v>2.7</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A56" s="1">
-        <v>18</v>
-      </c>
-      <c r="B56">
-        <v>748.74099999999999</v>
-      </c>
-      <c r="C56">
-        <v>2.7</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A57" s="1"/>
-      <c r="B57">
-        <v>729.92600000000004</v>
-      </c>
-      <c r="C57">
-        <v>2.7</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A58" s="1"/>
-      <c r="B58">
-        <v>728.34500000000003</v>
-      </c>
-      <c r="C58">
-        <v>2.7</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A59" s="1">
-        <v>19</v>
-      </c>
-      <c r="B59">
-        <v>347.68299999999999</v>
-      </c>
-      <c r="C59">
-        <v>2.7</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A60" s="1"/>
-      <c r="B60">
-        <v>347.709</v>
-      </c>
-      <c r="C60">
-        <v>2.7</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A61" s="1"/>
-      <c r="B61">
-        <v>354.70800000000003</v>
-      </c>
-      <c r="C61">
-        <v>2.7</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="20">
-    <mergeCell ref="A56:A58"/>
-    <mergeCell ref="A59:A61"/>
-    <mergeCell ref="A38:A40"/>
-    <mergeCell ref="A41:A43"/>
-    <mergeCell ref="A44:A46"/>
-    <mergeCell ref="A47:A49"/>
-    <mergeCell ref="A50:A52"/>
-    <mergeCell ref="A53:A55"/>
-    <mergeCell ref="A35:A37"/>
+  <mergeCells count="9">
+    <mergeCell ref="A17:A19"/>
+    <mergeCell ref="A20:A22"/>
+    <mergeCell ref="A23:A25"/>
+    <mergeCell ref="A26:A28"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="A5:A7"/>
     <mergeCell ref="A8:A10"/>
     <mergeCell ref="A11:A13"/>
     <mergeCell ref="A14:A16"/>
-    <mergeCell ref="A17:A19"/>
-    <mergeCell ref="A20:A22"/>
-    <mergeCell ref="A23:A25"/>
-    <mergeCell ref="A26:A28"/>
-    <mergeCell ref="A29:A31"/>
-    <mergeCell ref="A32:A34"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2040,7 +1716,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8A4D5F0-9731-0841-9FD6-6AFB115D6FA8}">
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
@@ -2056,7 +1732,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>21.558</v>
+        <v>17.521999999999998</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
@@ -2064,7 +1740,7 @@
         <v>2.5</v>
       </c>
       <c r="B3">
-        <v>48.466000000000001</v>
+        <v>36.381</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
@@ -2072,7 +1748,7 @@
         <v>5</v>
       </c>
       <c r="B4">
-        <v>94.757000000000005</v>
+        <v>98.662000000000006</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
@@ -2080,7 +1756,7 @@
         <v>10</v>
       </c>
       <c r="B5">
-        <v>196.08099999999999</v>
+        <v>206.548</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
@@ -2088,7 +1764,7 @@
         <v>25</v>
       </c>
       <c r="B6">
-        <v>469.84800000000001</v>
+        <v>521.18399999999997</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
@@ -2096,7 +1772,7 @@
         <v>50</v>
       </c>
       <c r="B7">
-        <v>915.255</v>
+        <v>1074.355</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
@@ -2104,15 +1780,23 @@
         <v>100</v>
       </c>
       <c r="B8">
-        <v>1838.3109999999999</v>
+        <v>2136.6</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9">
+        <v>250</v>
+      </c>
+      <c r="B9">
+        <v>5092.2259999999997</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10">
         <v>500</v>
       </c>
-      <c r="B9">
-        <v>8983.7710000000006</v>
+      <c r="B10">
+        <v>9989.6059999999998</v>
       </c>
     </row>
   </sheetData>
